--- a/output/stock_quant_scores/BABA_balance_df.xlsx
+++ b/output/stock_quant_scores/BABA_balance_df.xlsx
@@ -1907,17 +1907,23 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>176597000000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>254751000000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>948479000000</v>
+      </c>
       <c r="Q6" t="n">
         <v>-47000000</v>
       </c>
@@ -1926,11 +1932,15 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>563557000000</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>613360000000</v>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
@@ -1942,7 +1952,9 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>383784000000</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -1960,7 +1972,9 @@
       <c r="AZ6" t="n">
         <v>94368000000</v>
       </c>
-      <c r="BA6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>1695553000000</v>
+      </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
@@ -1983,12 +1997,16 @@
       <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
+      <c r="BV6" t="n">
+        <v>638535000000</v>
+      </c>
       <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
-      <c r="CA6" t="inlineStr"/>
+      <c r="CA6" t="n">
+        <v>30087000000</v>
+      </c>
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
@@ -1997,7 +2015,9 @@
       <c r="CG6" t="inlineStr"/>
       <c r="CH6" t="inlineStr"/>
       <c r="CI6" t="inlineStr"/>
-      <c r="CJ6" t="inlineStr"/>
+      <c r="CJ6" t="n">
+        <v>189898000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
